--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.2936339836573</v>
+        <v>7.035215522344312</v>
       </c>
       <c r="D2" t="n">
-        <v>43.2575545342799</v>
+        <v>7.029352611820483</v>
       </c>
       <c r="E2" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F2" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.41263215612569</v>
+        <v>5.104552725370424</v>
       </c>
       <c r="D3" t="n">
-        <v>31.31288856453051</v>
+        <v>5.088344391736209</v>
       </c>
       <c r="E3" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F3" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.03296202092084</v>
+        <v>4.880356328399637</v>
       </c>
       <c r="D4" t="n">
-        <v>29.93050324788505</v>
+        <v>4.863706777781321</v>
       </c>
       <c r="E4" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F4" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.01921141991708</v>
+        <v>3.740621855736527</v>
       </c>
       <c r="D5" t="n">
-        <v>23.02302266090582</v>
+        <v>3.741241182397196</v>
       </c>
       <c r="E5" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F5" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.77745173343161</v>
+        <v>2.401335906682637</v>
       </c>
       <c r="D6" t="n">
-        <v>14.67959961159909</v>
+        <v>2.385434936884853</v>
       </c>
       <c r="E6" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F6" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.23165766883098</v>
+        <v>6.537644371185034</v>
       </c>
       <c r="D7" t="n">
-        <v>40.15662381395311</v>
+        <v>6.525451369767381</v>
       </c>
       <c r="E7" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F7" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.898322969213178</v>
+        <v>0.9584774824971415</v>
       </c>
       <c r="D8" t="n">
-        <v>5.968104474026522</v>
+        <v>0.9698169770293099</v>
       </c>
       <c r="E8" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F8" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.49459497675882</v>
+        <v>2.842871683723307</v>
       </c>
       <c r="D9" t="n">
-        <v>17.43483712063826</v>
+        <v>2.833161032103718</v>
       </c>
       <c r="E9" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F9" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.74528146133554</v>
+        <v>6.783608237467027</v>
       </c>
       <c r="D10" t="n">
-        <v>41.79969371003406</v>
+        <v>6.792450227880535</v>
       </c>
       <c r="E10" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F10" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.72808385871382</v>
+        <v>5.805813627040997</v>
       </c>
       <c r="D11" t="n">
-        <v>35.70547325681432</v>
+        <v>5.802139404232326</v>
       </c>
       <c r="E11" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F11" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.85989406479957</v>
+        <v>7.93973278552993</v>
       </c>
       <c r="D12" t="n">
-        <v>48.83986109311286</v>
+        <v>7.93647742763084</v>
       </c>
       <c r="E12" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F12" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.50721802157901</v>
+        <v>6.09492292850659</v>
       </c>
       <c r="D13" t="n">
-        <v>37.6041718276754</v>
+        <v>6.110677921997253</v>
       </c>
       <c r="E13" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F13" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.5882595248687</v>
+        <v>5.295592172791164</v>
       </c>
       <c r="D14" t="n">
-        <v>32.68571027657365</v>
+        <v>5.311427919943219</v>
       </c>
       <c r="E14" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F14" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>47.52958198895322</v>
+        <v>7.723557073204899</v>
       </c>
       <c r="D15" t="n">
-        <v>47.54127318150646</v>
+        <v>7.7254568919948</v>
       </c>
       <c r="E15" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F15" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.92482073082977</v>
+        <v>5.187783368759837</v>
       </c>
       <c r="D16" t="n">
-        <v>31.41517460382515</v>
+        <v>5.104965873121587</v>
       </c>
       <c r="E16" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F16" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37.78824915501063</v>
+        <v>6.140590487689227</v>
       </c>
       <c r="D17" t="n">
-        <v>37.66203299228647</v>
+        <v>6.120080361246552</v>
       </c>
       <c r="E17" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F17" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>17.83749220769256</v>
+        <v>2.89859248375004</v>
       </c>
       <c r="D18" t="n">
-        <v>17.25718473022633</v>
+        <v>2.804292518661779</v>
       </c>
       <c r="E18" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F18" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>30.17939663673591</v>
+        <v>4.904151953469585</v>
       </c>
       <c r="D19" t="n">
-        <v>30.08061533800757</v>
+        <v>4.88809999242623</v>
       </c>
       <c r="E19" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F19" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>39.18666596207279</v>
+        <v>6.367833218836828</v>
       </c>
       <c r="D20" t="n">
-        <v>39.38522517901253</v>
+        <v>6.400099091589536</v>
       </c>
       <c r="E20" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F20" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>27.95022544939366</v>
+        <v>4.54191163552647</v>
       </c>
       <c r="D21" t="n">
-        <v>28.24747652844854</v>
+        <v>4.590214935872889</v>
       </c>
       <c r="E21" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F21" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>31.62779807190622</v>
+        <v>5.139517186684761</v>
       </c>
       <c r="D22" t="n">
-        <v>32.12148790217578</v>
+        <v>5.219741784103564</v>
       </c>
       <c r="E22" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F22" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>40.14485891352776</v>
+        <v>6.523539573448262</v>
       </c>
       <c r="D23" t="n">
-        <v>40.68460454161354</v>
+        <v>6.6112482380122</v>
       </c>
       <c r="E23" t="n">
-        <v>10.67078678015782</v>
+        <v>1.734002851775646</v>
       </c>
       <c r="F23" t="n">
-        <v>10.72867495116631</v>
+        <v>1.743409679564525</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
